--- a/public/lessons_batch_sample.xlsx
+++ b/public/lessons_batch_sample.xlsx
@@ -450,12 +450,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
     <col min="3" max="3" width="28.83203125" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,6 +473,12 @@
       <c r="D1" t="str">
         <v>Meaning EN</v>
       </c>
+      <c r="E1" t="str">
+        <v>Reading</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Audio Filename</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -485,6 +493,12 @@
       <c r="D2" t="str">
         <v>Hello</v>
       </c>
+      <c r="E2" t="str">
+        <v>こんにちは</v>
+      </c>
+      <c r="F2" t="str">
+        <v>n5_l01_v01.mp3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -499,6 +513,12 @@
       <c r="D3" t="str">
         <v>Thank you</v>
       </c>
+      <c r="E3" t="str">
+        <v>ありがとう</v>
+      </c>
+      <c r="F3" t="str">
+        <v>n5_l01_v02.mp3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -513,10 +533,16 @@
       <c r="D4" t="str">
         <v>Mother</v>
       </c>
+      <c r="E4" t="str">
+        <v>おかあさん</v>
+      </c>
+      <c r="F4" t="str">
+        <v>n5_l02_v01.mp3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,12 +608,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
     <col min="3" max="3" width="28.83203125" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -603,6 +630,9 @@
       <c r="D1" t="str">
         <v>Translation MM</v>
       </c>
+      <c r="E1" t="str">
+        <v>Audio Filename</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -617,6 +647,9 @@
       <c r="D2" t="str">
         <v>ကျောင်းသားပါ။</v>
       </c>
+      <c r="E2" t="str">
+        <v>n5_l01_ge01.mp3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -631,17 +664,20 @@
       <c r="D3" t="str">
         <v>ကျွန်တော့်အမေပါ။</v>
       </c>
+      <c r="E3" t="str">
+        <v>n5_l02_ge01.mp3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -653,6 +689,8 @@
     <col min="8" max="8" width="28.83203125" customWidth="1"/>
     <col min="9" max="9" width="28.83203125" customWidth="1"/>
     <col min="10" max="10" width="28.83203125" customWidth="1"/>
+    <col min="11" max="11" width="28.83203125" customWidth="1"/>
+    <col min="12" max="12" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -686,6 +724,12 @@
       <c r="J1" t="str">
         <v>Explain EN</v>
       </c>
+      <c r="K1" t="str">
+        <v>Transcript</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Audio Filename</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -718,6 +762,12 @@
       <c r="J2" t="str">
         <v>Hello is こんにちは.</v>
       </c>
+      <c r="K2" t="str">
+        <v>こんにちは。わたしは たなかです。</v>
+      </c>
+      <c r="L2" t="str">
+        <v>n5_l01_q01.mp3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -750,10 +800,16 @@
       <c r="J3" t="str">
         <v>おかあさん means mother.</v>
       </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>